--- a/EKG_Kalite_Yönetim_Sistemi/15_Katmanlı Denetim ve Yetkinlik/01_LPASK1-2 - LPA, Takvim ve Karşı Önlem/EKG-KLT-PLN-09_lpa_plani_ve_istasyon_imza_cizelgesi.xlsx
+++ b/EKG_Kalite_Yönetim_Sistemi/15_Katmanlı Denetim ve Yetkinlik/01_LPASK1-2 - LPA, Takvim ve Karşı Önlem/EKG-KLT-PLN-09_lpa_plani_ve_istasyon_imza_cizelgesi.xlsx
@@ -779,7 +779,8 @@
   <pageSetup scale="100"/>
   <headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="0" alignWithMargins="1">
     <oddHeader>&amp;L&amp;"Arial,Bold"&amp;11EKG-KLT-PLN-09&amp;C&amp;"Arial,Regular"&amp;11LPA Planı ve İstasyon İmza Çizelgesi</oddHeader>
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 04.05.2026 | Revizyon: 19.10.2026&amp;R&amp;11Sayfa &amp;P / &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 03.06.2026 | Revizyon: 07.09.2026
+Revizyon nedeni: Takvim, fiili tarih, kontrol kaydı ve faaliyet bağlantısı netleştirildi.&amp;R&amp;11Sayfa &amp;P / &amp;N</oddFooter>
   </headerFooter>
 </worksheet>
 </file>
@@ -931,7 +932,8 @@
   <pageSetup scale="100"/>
   <headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="0" alignWithMargins="1">
     <oddHeader>&amp;L&amp;"Arial,Bold"&amp;11EKG-KLT-PLN-09&amp;C&amp;"Arial,Regular"&amp;11LPA Planı ve İstasyon İmza Çizelgesi</oddHeader>
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 04.05.2026 | Revizyon: 19.10.2026&amp;R&amp;11Sayfa &amp;P / &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 03.06.2026 | Revizyon: 07.09.2026
+Revizyon nedeni: Takvim, fiili tarih, kontrol kaydı ve faaliyet bağlantısı netleştirildi.&amp;R&amp;11Sayfa &amp;P / &amp;N</oddFooter>
   </headerFooter>
 </worksheet>
 </file>